--- a/model_templates/ark.SpatialImagingAssayMetadataTemplate.xlsx
+++ b/model_templates/ark.SpatialImagingAssayMetadataTemplate.xlsx
@@ -3,8 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
-    <sheet state="hidden" name="Sheet2" sheetId="2" r:id="rId5"/>
+    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet state="hidden" name="Sheet2" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -5067,7 +5067,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="21">
   <si>
     <t>Component</t>
   </si>
@@ -5115,6 +5115,9 @@
   </si>
   <si>
     <t>H&amp;E</t>
+  </si>
+  <si>
+    <t>unknown</t>
   </si>
   <si>
     <t>imaging mass cytometry</t>
@@ -5239,6 +5242,10 @@
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -32489,7 +32496,7 @@
   </conditionalFormatting>
   <dataValidations>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="C2:C1000">
-      <formula1>Sheet2!$C$2:$C$3</formula1>
+      <formula1>Sheet2!$C$2:$C$4</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="B2:B1000">
       <formula1>Sheet2!$B$2:$B$8</formula1>
@@ -32559,25 +32566,28 @@
       <c r="B4" s="7" t="s">
         <v>15</v>
       </c>
+      <c r="C4" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="5">
       <c r="B5" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/model_templates/ark.SpatialImagingAssayMetadataTemplate.xlsx
+++ b/model_templates/ark.SpatialImagingAssayMetadataTemplate.xlsx
@@ -32484,14 +32484,14 @@
       <c r="Y1000" s="6"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="J1:J1000">
+  <conditionalFormatting sqref="I1:I1000">
     <cfRule type="expression" dxfId="0" priority="1" stopIfTrue="1">
-      <formula>$C1 = "multispecimen"</formula>
+      <formula>$C1 = "single specimen"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I1000">
+  <conditionalFormatting sqref="J1:J1000">
     <cfRule type="expression" dxfId="0" priority="2" stopIfTrue="1">
-      <formula>$C1 = "single specimen"</formula>
+      <formula>$C1 = "multispecimen"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
